--- a/CHARMS CLIPS Y TOPES.xlsx
+++ b/CHARMS CLIPS Y TOPES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A202FE3F-B763-4114-841A-E5DDDF926CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B04CEDD3-4F2C-404F-B7D6-00B34869D5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DB857668-31C1-472D-90DD-19934E52BBA6}"/>
   </bookViews>
@@ -7666,7 +7666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4481F961-2A19-4F0F-9DE8-FB0FBB4A576C}">
-  <dimension ref="A1:K289"/>
+  <dimension ref="A1:K287"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3" customWidth="1"/>
@@ -7976,9 +7976,7 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="I11" s="10">
-        <v>2</v>
-      </c>
+      <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
     </row>
@@ -8007,9 +8005,7 @@
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="10">
-        <v>1</v>
-      </c>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="63.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
@@ -8088,9 +8084,7 @@
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
+      <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
     </row>
@@ -12144,130 +12138,128 @@
       <c r="J165" s="10"/>
       <c r="K165" s="10"/>
     </row>
-    <row r="166" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" spans="1:11" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" s="3" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
